--- a/data/processed/my_album_status.xlsx
+++ b/data/processed/my_album_status.xlsx
@@ -2537,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:M133"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
@@ -2597,7 +2597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:13">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:13">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:13">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:13">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:13">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:13">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:13">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:13">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:13">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:12">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:12">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:12">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:12">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:12">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>108</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:12">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>116</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:12">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" hidden="1" spans="1:12">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:12">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:12">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:12">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="1:12">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="1:12">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" hidden="1" spans="1:12">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>161</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="1:12">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>163</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="1:12">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="1:12">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>179</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:12">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>183</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:12">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:12">
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>194</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:12">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>202</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:12">
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>204</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:12">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>208</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:12">
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>212</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:12">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>214</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:12">
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:12">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>42</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:12">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:12">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>234</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:12">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:12">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>249</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:12">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>253</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:12">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>255</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:12">
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:12">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>264</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:12">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>149</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:12">
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:12">
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
         <v>42</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:12">
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
         <v>277</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:12">
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
         <v>281</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:12">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
         <v>291</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:12">
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
         <v>171</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:12">
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
         <v>297</v>
       </c>
@@ -5453,7 +5453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:12">
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
         <v>301</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:12">
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
         <v>305</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:12">
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>307</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:12">
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
         <v>311</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:12">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
         <v>321</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:12">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
         <v>149</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:12">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
         <v>336</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:12">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
         <v>287</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:12">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>341</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:12">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:12">
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
         <v>346</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:12">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
         <v>346</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:12">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
         <v>357</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:12">
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
         <v>359</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:12">
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>363</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:12">
+    <row r="104" spans="1:12">
       <c r="A104" t="s">
         <v>365</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:12">
+    <row r="105" spans="1:12">
       <c r="A105" t="s">
         <v>369</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:12">
+    <row r="106" spans="1:12">
       <c r="A106" t="s">
         <v>373</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:12">
+    <row r="107" spans="1:12">
       <c r="A107" t="s">
         <v>377</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:12">
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
         <v>378</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:12">
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
         <v>85</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:12">
+    <row r="110" spans="1:12">
       <c r="A110" t="s">
         <v>204</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:12">
+    <row r="111" spans="1:12">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:12">
+    <row r="112" spans="1:12">
       <c r="A112" t="s">
         <v>391</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:12">
+    <row r="114" spans="1:12">
       <c r="A114" t="s">
         <v>399</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:12">
+    <row r="115" spans="1:12">
       <c r="A115" t="s">
         <v>198</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:12">
+    <row r="116" spans="1:12">
       <c r="A116" t="s">
         <v>321</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:12">
+    <row r="117" spans="1:12">
       <c r="A117" t="s">
         <v>391</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:12">
+    <row r="118" spans="1:12">
       <c r="A118" t="s">
         <v>198</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:12">
+    <row r="119" spans="1:12">
       <c r="A119" t="s">
         <v>321</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:12">
+    <row r="120" spans="1:12">
       <c r="A120" t="s">
         <v>412</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:12">
+    <row r="121" spans="1:12">
       <c r="A121" t="s">
         <v>416</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:12">
+    <row r="122" spans="1:12">
       <c r="A122" t="s">
         <v>420</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:12">
+    <row r="123" spans="1:12">
       <c r="A123" t="s">
         <v>424</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:12">
+    <row r="124" spans="1:12">
       <c r="A124" t="s">
         <v>253</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:12">
+    <row r="125" spans="1:12">
       <c r="A125" t="s">
         <v>429</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:12">
+    <row r="128" spans="1:12">
       <c r="A128" t="s">
         <v>439</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:12">
+    <row r="129" spans="1:12">
       <c r="A129" t="s">
         <v>441</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="1:12">
+    <row r="131" spans="1:12">
       <c r="A131" t="s">
         <v>108</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="1:12">
+    <row r="132" spans="1:12">
       <c r="A132" t="s">
         <v>447</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="1:12">
+    <row r="133" spans="1:12">
       <c r="A133" t="s">
         <v>81</v>
       </c>
@@ -7135,13 +7135,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M133" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="low"/>
-        <filter val="high"/>
-        <filter val="medium"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed/my_album_status.xlsx
+++ b/data/processed/my_album_status.xlsx
@@ -2537,19 +2537,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M133"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="33.1818181818182" customWidth="1"/>
     <col min="2" max="2" width="69.1818181818182" customWidth="1"/>
-    <col min="3" max="3" width="5.54545454545455" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54545454545454" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6363636363636" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.8181818181818" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="17.3636363636364" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20.8181818181818" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="142.272727272727" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.54545454545455" customWidth="1"/>
+    <col min="4" max="4" width="9.54545454545454" customWidth="1"/>
+    <col min="5" max="5" width="10.6363636363636" customWidth="1"/>
+    <col min="6" max="6" width="11.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="17.3636363636364" customWidth="1"/>
+    <col min="8" max="8" width="20.8181818181818" customWidth="1"/>
+    <col min="9" max="9" width="142.272727272727" customWidth="1"/>
     <col min="10" max="10" width="18.5454545454545" customWidth="1"/>
     <col min="11" max="11" width="17.3636363636364" customWidth="1"/>
     <col min="12" max="12" width="19.6363636363636" customWidth="1"/>
@@ -2635,7 +2635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" hidden="1" spans="1:13">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" hidden="1" spans="1:13">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" hidden="1" spans="1:13">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" hidden="1" spans="1:13">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" hidden="1" spans="1:13">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" hidden="1" spans="1:13">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" hidden="1" spans="1:13">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" hidden="1" spans="1:13">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" hidden="1" spans="1:13">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" hidden="1" spans="1:12">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" hidden="1" spans="1:12">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" hidden="1" spans="1:12">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" hidden="1" spans="1:12">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" hidden="1" spans="1:12">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" hidden="1" spans="1:12">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" hidden="1" spans="1:12">
       <c r="A26" t="s">
         <v>112</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" hidden="1" spans="1:12">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" hidden="1" spans="1:12">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" hidden="1" spans="1:12">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" hidden="1" spans="1:12">
       <c r="A33" t="s">
         <v>138</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" hidden="1" spans="1:12">
       <c r="A35" t="s">
         <v>145</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" hidden="1" spans="1:12">
       <c r="A36" t="s">
         <v>149</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" hidden="1" spans="1:12">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" hidden="1" spans="1:12">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" hidden="1" spans="1:12">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" hidden="1" spans="1:12">
       <c r="A42" t="s">
         <v>171</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" hidden="1" spans="1:12">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" hidden="1" spans="1:12">
       <c r="A44" t="s">
         <v>179</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" hidden="1" spans="1:12">
       <c r="A45" t="s">
         <v>183</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" hidden="1" spans="1:12">
       <c r="A46" t="s">
         <v>187</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" hidden="1" spans="1:12">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" hidden="1" spans="1:12">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" hidden="1" spans="1:12">
       <c r="A52" t="s">
         <v>206</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" hidden="1" spans="1:12">
       <c r="A55" t="s">
         <v>214</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" hidden="1" spans="1:12">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" hidden="1" spans="1:12">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" hidden="1" spans="1:12">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" hidden="1" spans="1:12">
       <c r="A60" t="s">
         <v>229</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" hidden="1" spans="1:12">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" hidden="1" spans="1:12">
       <c r="A64" t="s">
         <v>241</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" hidden="1" spans="1:12">
       <c r="A65" t="s">
         <v>245</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" hidden="1" spans="1:12">
       <c r="A66" t="s">
         <v>249</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" hidden="1" spans="1:12">
       <c r="A67" t="s">
         <v>253</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" hidden="1" spans="1:12">
       <c r="A69" t="s">
         <v>259</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" hidden="1" spans="1:12">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" hidden="1" spans="1:12">
       <c r="A77" t="s">
         <v>285</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" hidden="1" spans="1:12">
       <c r="A78" t="s">
         <v>287</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" hidden="1" spans="1:12">
       <c r="A80" t="s">
         <v>157</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" hidden="1" spans="1:12">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" hidden="1" spans="1:12">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" hidden="1" spans="1:12">
       <c r="A89" t="s">
         <v>319</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" hidden="1" spans="1:12">
       <c r="A90" t="s">
         <v>321</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" hidden="1" spans="1:12">
       <c r="A92" t="s">
         <v>328</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" hidden="1" spans="1:12">
       <c r="A93" t="s">
         <v>332</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" hidden="1" spans="1:12">
       <c r="A94" t="s">
         <v>336</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" hidden="1" spans="1:12">
       <c r="A95" t="s">
         <v>287</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" hidden="1" spans="1:12">
       <c r="A99" t="s">
         <v>350</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" hidden="1" spans="1:12">
       <c r="A105" t="s">
         <v>369</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" hidden="1" spans="1:12">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" hidden="1" spans="1:12">
       <c r="A113" t="s">
         <v>395</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" hidden="1" spans="1:12">
       <c r="A114" t="s">
         <v>399</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" hidden="1" spans="1:12">
       <c r="A115" t="s">
         <v>198</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" hidden="1" spans="1:12">
       <c r="A118" t="s">
         <v>198</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" hidden="1" spans="1:12">
       <c r="A119" t="s">
         <v>321</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" hidden="1" spans="1:12">
       <c r="A121" t="s">
         <v>416</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" hidden="1" spans="1:12">
       <c r="A122" t="s">
         <v>420</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" hidden="1" spans="1:12">
       <c r="A126" t="s">
         <v>433</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" hidden="1" spans="1:12">
       <c r="A127" t="s">
         <v>437</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" hidden="1" spans="1:12">
       <c r="A130" t="s">
         <v>445</v>
       </c>
@@ -7135,6 +7135,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M133" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="unheard"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
